--- a/base_prov_co/unidroga/unidroga_abbott_2026_10_09.xlsx
+++ b/base_prov_co/unidroga/unidroga_abbott_2026_10_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,65 +451,70 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>MARCA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>categoría</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seller</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ventas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>valoración</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reviews</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>title_count_characters</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>count_character_desc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>url_imagen</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>url_producto</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>disponibilidad</t>
         </is>
@@ -536,20 +541,19 @@
           <t>8427030008608</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -557,34 +561,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>38</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>501</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Ensure® está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveer  los nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435594-800-auto?v=639211257638000000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-vainilla-tarro-x-850-gr-7703186030108/p</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -611,20 +620,19 @@
           <t>7703186032157</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -632,34 +640,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>71</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>386</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Ensure® Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.  Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435575-800-auto?v=639064268756430000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-vainilla-tarro-x-850gr-tarrox400gr-ahorr20--7703186032157/p</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -686,20 +699,19 @@
           <t>8710428018670</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -707,34 +719,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>40</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>386</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Ensure® Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.  Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/377658-800-auto?v=639068798735170000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-vainilla-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -761,20 +778,19 @@
           <t>8427030008592</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -782,34 +798,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>38</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>386</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Ensure® Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.  Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435601-800-auto?v=638902736208770000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-vainilla-tarro-x-400-gr-8427030004549/p</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -836,20 +857,19 @@
           <t>8710428018717</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -857,34 +877,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>37</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>386</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Ensure® Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.  Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/377657-800-auto?v=639068798716930000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-fresa-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -911,20 +936,19 @@
           <t>8710428013859</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -932,34 +956,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>35</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>501</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Ensure® está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveer  los nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/470910-800-auto?v=639268185367230000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-fresa-tarro-x-850-gr-8710428013859/p</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -986,20 +1015,19 @@
           <t>8710428013873</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1007,34 +1035,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>35</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>548</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Ensure® alimento para proposito medicos especiales, está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveer  los nutrientes necesarios para apoyar la alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que ayuda a mejorar la función intestinal, está formulado con antioxidantes y vitaminas (C,E ), selenio y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435579-800-auto?v=638902738716900000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-fresa-tarro-x-400-gr-8710428013873/p</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1061,20 +1094,19 @@
           <t>8710428018694</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1082,34 +1114,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>41</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>386</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Ensure® Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.  Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/430683-800-auto?v=639068798754230000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-chocolate-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1136,20 +1173,19 @@
           <t>8427030003153</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1157,34 +1193,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>30</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>501</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Ensure® está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveer  los nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435618-800-auto?v=638902736419800000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-polvo-vainilla-tarro-x-400-gr-8427030003153/p</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1211,20 +1252,19 @@
           <t>8710428019561</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1232,34 +1272,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>4</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>40</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>386</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Ensure® Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.  Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/377658-800-auto?v=639068798735170000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-vainilla-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1286,20 +1331,19 @@
           <t>7703186031433</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1307,34 +1351,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>41</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>457</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Ensure Clinical es un alimento para propositos medicos especiales  para adultos  que presenten sarcopenia o caquexia asociada a desnutrición proteico-calórica moderada o severa asociada a una condición médica.   Aporta 1,5 Kcal/mL y está formulado con HMB, 28 vitaminas y minerales para apoyar su alimentación en adultos con una perdida mayor en masa muscular y que no logran suplir sus requerimientos nutricionales con una alimentación normal o modificada.</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435584-800-auto?v=638902736067330000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-clinical-liquido-vainilla-botella-x-220-ml-7703186031433/p</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1361,20 +1410,19 @@
           <t>8710428018861</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1382,34 +1430,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>36</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>407</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Ensure® Advance es un alimento para propositos medicos especiales, dirigido adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.  Formulado con CaHMB y proteína para apoyar los músculos, así como 28 vitaminas y minerales, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/378273-800-auto?v=639068799517430000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-cafe-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1436,20 +1489,19 @@
           <t>7703186341334</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1457,34 +1509,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>34</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>153</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/460630-800-auto?v=638905320143900000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-cafe-x-400-gr/p</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1511,20 +1568,19 @@
           <t>8710428011848</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1532,34 +1588,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>39</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>386</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Ensure® Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.  Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435576-800-auto?v=638902738671770000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-chocolate-tarro-x-400-gr-8710428011848/p</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1586,20 +1647,19 @@
           <t>8710428017987</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1607,34 +1667,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>31</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>493</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Ensure® Plus HN alimento para propositos medicos especiales, diseñada para adultos que están en riesgo nutricional o que experimentan pérdida de peso involuntaria asociada a una condición de salud. Es una fórmula nutricional alta en calorías (1.5 kcal/mL), que contiene una combinación de proteínas, 28 vitaminas y minerales, y un balance adecuado de ácidos grasos omega 3 y omega 6. Es ideal para ayudarte a mejorar tu estado nutricional y contribuir a una ganancia de masa corporal adecuada.</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/377337-800-auto?v=638890745107330000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-plus-hn-liquido-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1661,20 +1726,19 @@
           <t>7703186069917</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1682,34 +1746,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>27</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>71</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Nutrición especializada para pacientes con enfermedad pulmonar crónica.</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435610-800-auto?v=638951125856930000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pulmocare-liquido-tarro-x-8-onzas-7703186069917/p</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1736,20 +1805,19 @@
           <t>7703186030191</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1757,34 +1825,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>25</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>756</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>NEPRO BP LIQUIDO LATA X 237 ML en Tu Droguería Virtual. Alimentación especializada alta en calorías y proteínas, restringida en agua y electrolitos, diseñada especialmente para cubrir las necesidades únicas de los pacientes renales durante la diálisis, que ha demostrado clínicamente: Incrementar la albúmina y prealbúmina sérica, mejorar el estado nutricional, reducir las infecciones gastrointestinales, el sistema Carb Steady es una mezcla de hidratos de carbono que evita los picos de glicemia en el organismo. El aporte de proteínas de alto valor biológico es la cantidad adecuada para reponer la pérdida de proteínas en la diálisis y prevenir el catabolismo de las proteínas tisulares. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435597-800-auto?v=638981434955430000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/nepro-bp-liquido-lata-x-237-ml-7703186030191/p</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1811,20 +1884,19 @@
           <t>7703186030184</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1832,34 +1904,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>25</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>327</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>NEPRO AB LIQUIDO LATA X 237 ML en Tu Droguería Virtual. Nepro Ap es una formulación líquida diseñada especialmente para suplir las necesidades nutricionales de las personas en diálisis. Alto en calorías, moderado en proteínas y bajo en contenido de electrolitos. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435596-800-auto?v=638976247158400000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/nepro-ap-liquido-lata-x-237-ml-7703186030184/p</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1886,20 +1963,19 @@
           <t>8710428022790</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1907,34 +1983,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>33</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>153</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/457819-800-auto?v=638902729247000000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/prosure-liquido-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1961,20 +2042,19 @@
           <t>8699548993756</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1982,34 +2062,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>25</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>233</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Abound Orange caja x 30 sobres es un alimento de uso especial con HMB, arginina y glutamina para personas con heridas de difícil cicatrización incluyendo úlceras de presión, úlcera de pie diabético, heridas por quemaduras y cirugías.</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435580-800-auto?v=638964631802430000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/abound-orange-caja-x-30-sobres-8699548993756/p</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2036,20 +2121,19 @@
           <t>8427030008943</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2057,34 +2141,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>5</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>32</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>370</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Glucerna® te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol. Glucerna® es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna® actúa desde el primer día.</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/384847-800-auto?v=638902730885870000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-vainilla-x-850-gr/p</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2111,20 +2200,19 @@
           <t>7703186030283</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2132,34 +2220,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>5</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>34</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>370</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Glucerna® te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol. Glucerna® es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna® actúa desde el primer día.</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435595-800-auto?v=638902736184870000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-vainilla-botella-x-237-ml-7703186030283/p</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2186,20 +2279,19 @@
           <t>7703186499844</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2207,34 +2299,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>62</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>370</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Glucerna® te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol. Glucerna® es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna® actúa desde el primer día.</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/448862-800-auto?v=638913204450500000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-vainilla-x-850-gr---glucerna-polvo-vainilla-x-400-gr-precio-especial/p</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2261,20 +2358,19 @@
           <t>7703186032737</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2282,34 +2378,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>5</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>58</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>370</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Glucerna® te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol. Glucerna® es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna® actúa desde el primer día.</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/381589-800-auto?v=638902732597630000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-vainilla-botella-x-237-ml-pack-x-6-und/p</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2336,20 +2437,19 @@
           <t>7703186190376</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2357,34 +2457,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>97</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>153</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/457335-800-auto?v=638913205514800000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-vainilla-x-237-ml--6----glucerna-liquido-fresa-x-237-ml--2--oferta-20--descuento/p</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2411,20 +2516,19 @@
           <t>7703186031525</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2432,34 +2536,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
         <v>5</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>32</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>370</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Glucerna® te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol. Glucerna® es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna® actúa desde el primer día.</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435589-800-auto?v=638902736086900000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-fresa-botella-x-237-ml-7703186031525/p</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2486,20 +2595,19 @@
           <t>8427030008936</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2507,34 +2615,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
         <v>5</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>32</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>370</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Glucerna® te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol. Glucerna® es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna® actúa desde el primer día.</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435617-800-auto?v=638902736391330000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-vainilla-tarro-x-400-gr-7703186031594/p</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2561,20 +2674,19 @@
           <t>7703186358035</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2582,34 +2694,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>74</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>153</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/457340-800-auto?v=638913205533970000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-vainilla-x-400-gr-gratis-glucerna-liquido-vainilla-x-237-ml/p</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2636,20 +2753,19 @@
           <t>8427030009346</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2657,34 +2773,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>33</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>153</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/463040-800-auto?v=638967420162930000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-capuchino-x-400-gr/p</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2711,20 +2832,19 @@
           <t>8710428024299</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2732,34 +2852,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
         <v>5</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>43</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>153</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/457789-800-auto?v=638902729427400000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-1-6-kcal-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2786,20 +2911,19 @@
           <t>7501033957376</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2807,34 +2931,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>29</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>197</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Bebida que ayuda a prevenir los casos de deshidratacion en niños y adultos, causados por vomito, diarrea o actividad física intensa. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/431156-800-auto?v=638902736351670000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-60-uva-frasco-x-500-ml-7501033957376/p</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2861,20 +2990,19 @@
           <t>7501033961557</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2882,34 +3010,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>31</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>197</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Bebida que ayuda a prevenir los casos de deshidratacion en niños y adultos, causados por vomito, diarrea o actividad física intensa. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/369599-800-auto?v=638902738646700000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-60-fresa-frasco-x-500-ml-7501033961557/p</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2936,20 +3069,19 @@
           <t>7501033957369</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2957,34 +3089,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>33</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>197</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Bebida que ayuda a prevenir los casos de deshidratacion en niños y adultos, causados por vomito, diarrea o actividad física intensa. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/369576-800-auto?v=638902736364670000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-60-manzana-frasco-x-500-ml-7501033957369/p</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3011,20 +3148,19 @@
           <t>7501033961540</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3032,34 +3168,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>30</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>197</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Bebida que ayuda a prevenir los casos de deshidratacion en niños y adultos, causados por vomito, diarrea o actividad física intensa. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/369575-800-auto?v=638902738633900000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-60-coco-frasco-x-500-ml-7501033961540/p</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3086,20 +3227,19 @@
           <t>7501033959967</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3107,34 +3247,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>35</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>197</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Bebida que ayuda a prevenir los casos de deshidratacion en niños y adultos, causados por vomito, diarrea o actividad física intensa. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/369602-800-auto?v=638902736124630000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-30-cereza-frasco-x-500-ml-7501033959967/p</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3161,20 +3306,19 @@
           <t>7501033957413</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3182,34 +3326,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>34</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>197</v>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Bebida que ayuda a prevenir los casos de deshidratacion en niños y adultos, causados por vomito, diarrea o actividad física intensa. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/431158-800-auto?v=638902736378170000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-45-fresa-frasco-x-500-ml-7501033957413/p</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3236,20 +3385,19 @@
           <t>7501033959974</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3257,34 +3405,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>33</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>197</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Bebida que ayuda a prevenir los casos de deshidratacion en niños y adultos, causados por vomito, diarrea o actividad física intensa. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/382721-800-auto?v=638902736149600000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-30-coco-frasco-x-500-ml-7501033959974/p</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3311,20 +3464,19 @@
           <t>7501033959950</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3332,34 +3484,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>47</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>143</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Compra ya! SUERO DE REH PEDIALYTE MANZANA FRASCO X 500 ML desde la comodidad de tu hogar, sin filas, paga contra entrega, efectivo y/o tarjeta.</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1883355-800-auto?v=639108424319730000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-30-manzana-115206/p</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3386,20 +3543,19 @@
           <t>7501033959981</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3407,34 +3563,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>47</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>143</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Compra ya! SUERO DE REH PEDIALYTE DURAZNO FRASCO X 500 ML desde la comodidad de tu hogar, sin filas, paga contra entrega, efectivo y/o tarjeta.</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1883360-800-auto?v=639108424935200000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-30-durazno-115208/p</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3461,20 +3622,19 @@
           <t>7501033962394</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3482,34 +3642,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>47</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>140</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Compra ya! SUERO REH PEDIALYTE GUARANA FRASCO X 500 ML desde la comodidad de tu hogar, sin filas, paga contra entrega, efectivo y/o tarjeta.</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1888333-800-auto?v=639110047304100000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-45-guarana-148796/p</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3536,20 +3701,19 @@
           <t>7703186000026</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3557,34 +3721,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>86</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>153</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/463870-800-auto?v=639041040173630000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-10--polvo-vainilla-x-850-gr-gratis-3-pediasure-10--liquido-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3611,20 +3780,19 @@
           <t>8886451012074</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3632,34 +3800,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
         <v>5</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>33</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>350</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure®, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure® ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas. ¹</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/456813-800-auto?v=638902729838430000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-vainilla-x-850-gr/p</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3686,20 +3859,19 @@
           <t>8886451007049</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3707,34 +3879,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
         <v>5</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>34</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>348</v>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure®, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure® ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/377779-800-auto?v=638907918169500000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-vainilla-tarro-x-1600-gr/p</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3761,20 +3938,19 @@
           <t>8710428020185</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3782,34 +3958,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>35</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>348</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure®, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure® ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/382398-800-auto?v=639058431308400000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-liquido-vainilla-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3836,20 +4017,19 @@
           <t>8710428020314</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3857,34 +4037,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
         <v>4</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>32</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>348</v>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure®, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure® ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/382395-800-auto?v=639058431286230000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-liquido-fresa-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3911,20 +4096,19 @@
           <t>8886451012036</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3932,34 +4116,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>5</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>39</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>153</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/457784-800-auto?v=638902729407570000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-fresa-x-850-gr/p</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3986,20 +4175,19 @@
           <t>8710428021885</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4007,34 +4195,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>37</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>153</v>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/460625-800-auto?v=638905320129300000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-10--polvo-vainilla-x-850-gr/p</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4061,20 +4254,19 @@
           <t>8886451012029</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4082,34 +4274,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>30</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>348</v>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure®, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure® ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435613-800-auto?v=638890751083930000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-fresa-tarro-x-400-gr-7703186027580/p</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4136,20 +4333,19 @@
           <t>7703186799036</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4157,34 +4353,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
         <v>2</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>76</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>153</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/457183-800-auto?v=638913205619400000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-vainilla-x-400-gr-gratis-pediasure-liquido-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4211,20 +4412,19 @@
           <t>7703186033130</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4232,34 +4432,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
         <v>5</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>64</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>348</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure®, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure® ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/381204-800-auto?v=638902731693800000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-liquido-vainilla-botella-x-220-ml-pack-x-6-und/p</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4286,20 +4491,19 @@
           <t>7703186123480</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4307,34 +4511,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
         <v>2</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
       <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
         <v>64</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>153</v>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/457355-800-auto?v=638913205600270000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-liquido-vainilla-x-220-ml-x-8-und-oferta-20--descuento/p</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4361,20 +4570,19 @@
           <t>8710428024039</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4382,34 +4590,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>39</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>153</v>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/460620-800-auto?v=638905320107870000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-10--liquido-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4436,20 +4649,19 @@
           <t>5099864016987</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4457,34 +4669,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>35</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>158</v>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Fórmula infantil con hierro para lactantes de 0 a 6 meses, con una combinación de grasas fácil digestión, 5 HMOs (oligosacáridos), nucleótidos, DHA y luteína.</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/381213-800-auto?v=638891178958470000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-1-tarro-x-350-gr/p</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4511,20 +4728,19 @@
           <t>5099864016994</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4532,34 +4748,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
         <v>1</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>35</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>358</v>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>La Fórmula Infantil Similac, presentada en una lata de 800 gr, es un alimento especialmente diseñado para bebés. Esta fórmula puede ofrecer los nutrientes esenciales para el crecimiento y desarrollo saludable de los lactantes. Asegúrate de seguir las indicaciones proporcionadas por el pediatra y consultar con profesionales de la salud para un uso adecuado.</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/381212-800-auto?v=638891178947100000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-1-tarro-x-800-gr/p</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4586,20 +4807,19 @@
           <t>7703186863072</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4607,34 +4827,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
         <v>1</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
         <v>36</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>175</v>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Fórmula infantil con hierro para lactantes de 0 a 6 meses que combina una mezcla de grasas de fácil digestión. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435591-800-auto?v=639041153728370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-1-caja-x-1400-gr-7703186031860/p</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4661,20 +4886,19 @@
           <t>7703186497345</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4682,34 +4906,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
         <v>1</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>59</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>168</v>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Fórmula infantil líquida con hierro para lactantes de 0 a 6 meses con una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos), nucleótidos, DHA y luteína.</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/384452-800-auto?v=638891179247370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/formula-infantil-similac-1-liquido-x-8-botellas-x-59-ml-c-u/p</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4736,20 +4965,19 @@
           <t>5099864017021</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4757,34 +4985,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
         <v>1</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
         <v>36</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>266</v>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>La fórmula de Similac 2 está elaborada especialmente para los lactantes entre los 6 y 12 meses. Este producto está compuesto por luteína, DHL, nucleótidos y vitaminas que sirven para mejorar la digestión, fortalecer el sistema inmune e incitar al correcto desarrollo</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/375990-800-auto?v=638891182666000000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-2-tarro-x-1800-gr/p</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4811,20 +5044,19 @@
           <t>5099864017014</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4832,34 +5064,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>35</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>479</v>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>La Fórmula Infantil Similac 2 en lata de 800 g está especialmente formulada para proporcionar una nutrición completa y equilibrada para bebés. Enriquecida con nutrientes esenciales como DHA, luteína y vitamina E, esta fórmula apoya el desarrollo cerebral, la salud ocular y el sistema inmunológico de tu bebé. Su fácil digestión y delicioso sabor hacen de Similac 2 una excelente elección para complementar la alimentación de tu pequeño durante esta etapa crucial de crecimiento.</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/381210-800-auto?v=638891178924100000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-2-tarro-x-800-gr/p</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4886,20 +5123,19 @@
           <t>5099864017007</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4907,34 +5143,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
       <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
         <v>35</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>588</v>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>La Fórmula Infantil Similac 2, en su lata de 350 gramos, proporciona una nutrición completa y equilibrada para apoyar el crecimiento y desarrollo saludable de tu bebé. Esta fórmula está especialmente diseñada para bebés a partir de los 6 meses de edad, ofreciendo una combinación óptima de vitaminas, minerales y otros nutrientes esenciales para cubrir sus necesidades nutricionales en esta etapa crucial de crecimiento. La Fórmula Infantil Similac 2 es fácil de preparar y de digerir, asegurando que tu bebé reciba todos los nutrientes necesarios para su bienestar y desarrollo adecuado.</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/381211-800-auto?v=638891178935370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-2-tarro-x-350-gr/p</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4961,20 +5202,19 @@
           <t>5099864017229</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4982,34 +5222,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
         <v>5</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
       <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
         <v>35</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>397</v>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>El Alimento Lácteo Similac 3 es una fórmula infantil especialmente diseñada para niños a partir de los 12 meses de edad. Contiene una combinación de nutrientes que ayudan a satisfacer las necesidades de crecimiento y desarrollo de los pequeños.  Este alimento lácteo proporciona una nutrición completa y equilibrada, complementando la alimentación diaria de los niños en esta etapa de crecimiento.</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/437657-800-auto?v=638913646053670000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-3-tarro-x-1800-gr/p</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5036,20 +5281,19 @@
           <t>5099864017212</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5057,34 +5301,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
         <v>5</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
       <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
         <v>34</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>606</v>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>"A partir de los 2 años, los niños entran en una etapa llena de cambios, retos y mucho crecimiento. Similac 3 Kid está Fórmulado para apoyar ese momento clave, combinando una mezcla única de grasas de fácil digestión con ingredientes como 5 HMOs, nucleótidos, DHA, luteína, hierro, calcio y vitamina D.  Además, contiene probiótico y prebiótico, que junto con los 5 HMOs apoyan el buen funcionamiento del sistema inmune y gastrointestinal. Su fórmula está pensada para niños en crecimiento, ayudando a cubrir sus necesidades nutricionales mientras se preparan para nuevas etapas como el ingreso al jardín."</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/382420-800-auto?v=638902731650630000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-3-tarro-x-800-gr/p</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5111,20 +5360,19 @@
           <t>5099864017205</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5132,34 +5380,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
         <v>5</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
       <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>34</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>644</v>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>El alimento lácteo Similac 3 es una opción confiable para la nutrición completa de tu pequeño. Esta lata de 350 gramos contiene una fórmula especialmente diseñada para niños en crecimiento, proporcionando los nutrientes esenciales que necesitan para un desarrollo saludable. Con una combinación equilibrada de vitaminas, minerales y proteínas, el Similac 3 ayuda a fortalecer el sistema inmunológico, favorece el crecimiento adecuado y apoya el desarrollo cognitivo. Además, su fácil preparación lo convierte en una opción práctica para los padres ocupados. Asegúrate de brindar a tu pequeño la mejor nutrición con el alimento lácteo Similac 3.</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/419475-800-auto?v=638902731671870000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-3-tarro-x-350-gr/p</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5186,20 +5439,19 @@
           <t>8427030005003</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5207,34 +5459,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
         <v>36</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>774</v>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Nuestra lata de 850 gramos de Fórmula Infantil Similac AR es la elección perfecta para bebés que experimentan regurgitación o reflujo gastroesofágico. Similac AR ha sido especialmente formulada para reducir la frecuencia y la gravedad de la regurgitación, proporcionando alivio tanto a los bebés como a los padres. Esta fórmula contiene una mezcla única de nutrientes y espesantes que ayudan a mantener la leche en el estómago, reduciendo así la posibilidad de que vuelva a subir. Además, Similac AR proporciona todos los nutrientes esenciales que tu bebé necesita para un crecimiento y desarrollo saludables. Si buscas una fórmula infantil de calidad que ayude a tu bebé a sentirse más cómodo y satisfecho, confía en Similac AR. Brinda a tu pequeño el alivio que se merece.</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435599-800-auto?v=639041153797230000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-ar-tarro--x-850-gr-8427030005003/p</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5261,20 +5518,19 @@
           <t>8427030004938</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5282,34 +5538,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
         <v>1</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
       <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>36</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>158</v>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Formula láctea para el manejo del reflujo con AA y DHA para lactantes desde 0 hasta 12 meses. Envío a domicilio a nivel nacional. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435600-800-auto?v=639041153808070000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-ar-tarro--x-375-gr-8427030004938/p</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5336,20 +5597,19 @@
           <t>7703186029508</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5357,34 +5617,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
         <v>1</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
       <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>21</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>171</v>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Alimento a base de leche en polvo descremada, con vitaminas y minerales para mujeres embarazadas y en periodo de lactancia. Envío a domicilio. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435602-800-auto?v=638926283126300000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-mama-tarro-x-400-gr-7703186029508/p</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5411,20 +5676,19 @@
           <t>7703186032836</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5432,34 +5696,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
         <v>1</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
         <v>48</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>438</v>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>Asegura la nutrición óptima para tu bebé con la Fórmula Infantil Similac Mamá. Este paquete incluye 2 latas de 400 gramos cada una, ofreciendo un ahorro del 20% en tu compra. Desarrollada con ingredientes cuidadosamente seleccionados, Similac Mamá proporciona los nutrientes esenciales para el crecimiento saludable durante el periodo de lactancia. Aprovecha esta oferta y garantiza la mejor alimentación para tu pequeño con Similac Mamá.</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435577-800-auto?v=638986724001970000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-mama-tarro-x-400-gr--2--20--descuento-7703186032836/p</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5486,20 +5755,19 @@
           <t>8427030003658</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5507,34 +5775,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
       <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
         <v>41</v>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
         <v>199</v>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Fórmula con hierro para lactantes prematuros y/o lactantes con bajo peso al nacer para ser usada despues del alta hospitalaria de 0 a 12 meses de edad. Envío a domicilio. Pide online al mejor precio.</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435607-800-auto?v=639258995207370000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-neosure-tarro--x-370-gr-8427030003658/p</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5561,20 +5834,19 @@
           <t>5099864017236</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5582,34 +5854,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
       <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
         <v>49</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>437</v>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>La fórmula infantil Similac Rice está especialmente diseñada para bebés de 0 a 12 meses y se presenta en una lata de 400 gramos. Esta fórmula proporciona una nutrición esencial y balanceada para el crecimiento y desarrollo saludable de tu bebé.  Similac Rice está enriquecida con nutrientes clave, incluyendo hierro, calcio, vitaminas y minerales esenciales para apoyar el desarrollo cognitivo, óseo y el sistema inmunológico de tu bebé.</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/380676-800-auto?v=638891179311700000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-rice-0-12-meses-tarro-x-400-gr/p</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5636,20 +5913,19 @@
           <t>8427030003238</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5657,34 +5933,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
       <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
         <v>45</v>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
         <v>318</v>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>Similac es una fórmula especialmente diseñada para cuidar el sistema digestivo de los lactantes que tienen intolerancia transitoria a la lactosa y/o intolerancia a la proteína entera de la leche. para lactantes con necesidades especiales de nutrición como riesgo a desarrollar alergia a la proteína entera de la leche.</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435608-800-auto?v=639041153879900000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-sin-lactosa-tarro--x-375-gr-8427030003238/p</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5711,20 +5992,19 @@
           <t>8427030008820</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5732,34 +6012,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
       <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
         <v>53</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>286</v>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>"Alimento lácteo, bajo en lactosa, con proteína parcialmente hidrolizada, mezcla de grasas de fácil digestión, prebiótico HMO 2'-FL, DHA y luteína para niños de 1 a 3 años.  Agrega 26,5 gr de la Fórmula infantil similac total comfort 2 prosensitive en 180 ml de agua, mezcla y consume."</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/437005-800-auto?v=638891176544070000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/formula-infantil-similac-2-total-comfort-kid-lata-x-820-gr/p</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5786,20 +6071,19 @@
           <t>7703186032355</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5807,34 +6091,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
       <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
         <v>50</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>376</v>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>Similac Total Comfort 1 es una fórmula especialmente diseñada para cuidar el sistema digestivo de los lactantes, Sugerida para lactantes de 0 a 12 meses que tienen intolerancia transitoria a la lactosa y/o intolerancia a la proteína entera de la leche. para lactantes con necesidades especiales de nutrición como  riesgo a desarrollar alergia a la proteína entera de la leche.</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/435588-800-auto?v=639041153700930000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-total-comfort-1-caja-x-1400-gr-7703186032355/p</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5861,20 +6150,19 @@
           <t>8427030009285</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5882,34 +6170,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
         <v>49</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>153</v>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/463483-800-auto?v=639003024115200000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/formula-infantil-similac-1-total-comfort-x-800-gr/p</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5936,20 +6229,19 @@
           <t>8427030009278</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5957,34 +6249,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
       <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
         <v>49</v>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
         <v>153</v>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>Encuentra tus medicamentos, productos de salud, dermocosmética, belleza y cuidado personal en línea. Compra segura y envío ágil en Tudrogueriavirtual.com</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>https://unidrogas.vtexassets.com/arquivos/ids/464323-800-auto?v=639058536128970000&amp;width=800&amp;height=auto&amp;aspect=true</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/formula-infantil-similac-1-total-comfort-x-350-gr/p</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
